--- a/AtchisonRegime/Outputs/Euro/df_regZScores_Euro.xlsx
+++ b/AtchisonRegime/Outputs/Euro/df_regZScores_Euro.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6062,7 +6062,7 @@
         <v>-1.173508054480522</v>
       </c>
       <c r="C331" t="n">
-        <v>0.07440878746934976</v>
+        <v>0.003059559528599793</v>
       </c>
       <c r="D331" t="n">
         <v>0.6607631425232638</v>
@@ -6079,7 +6079,7 @@
         <v>-1.176877030846902</v>
       </c>
       <c r="C332" t="n">
-        <v>0.0780392389232072</v>
+        <v>0.06963252061712617</v>
       </c>
       <c r="D332" t="n">
         <v>0.6738196246178002</v>
@@ -6096,7 +6096,7 @@
         <v>-1.162274350584444</v>
       </c>
       <c r="C333" t="n">
-        <v>0.07326265395948543</v>
+        <v>0.06271089526937522</v>
       </c>
       <c r="D333" t="n">
         <v>0.64392862120351</v>
@@ -6113,7 +6113,7 @@
         <v>-1.192124318497693</v>
       </c>
       <c r="C334" t="n">
-        <v>0.05790582692168544</v>
+        <v>0.04690694013080018</v>
       </c>
       <c r="D334" t="n">
         <v>0.5453937035152667</v>
@@ -6130,7 +6130,7 @@
         <v>-1.247901006063838</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.05170998467301801</v>
+        <v>0.03049422547834524</v>
       </c>
       <c r="D335" t="n">
         <v>0.4012988812070913</v>
@@ -6147,7 +6147,7 @@
         <v>-1.274041300528749</v>
       </c>
       <c r="C336" t="n">
-        <v>0.01934764035298829</v>
+        <v>0.02255665395177126</v>
       </c>
       <c r="D336" t="n">
         <v>0.2692656463854147</v>
@@ -6164,7 +6164,7 @@
         <v>-1.224213763458834</v>
       </c>
       <c r="C337" t="n">
-        <v>0.03207639871494124</v>
+        <v>0.02775436740155613</v>
       </c>
       <c r="D337" t="n">
         <v>0.2201519689621168</v>
@@ -6181,7 +6181,7 @@
         <v>-1.100583367531713</v>
       </c>
       <c r="C338" t="n">
-        <v>0.04710340453708419</v>
+        <v>0.04565116666107294</v>
       </c>
       <c r="D338" t="n">
         <v>0.1470370271165108</v>
@@ -6198,7 +6198,7 @@
         <v>-1.004917433510945</v>
       </c>
       <c r="C339" t="n">
-        <v>0.08885128292497106</v>
+        <v>0.07696715706128913</v>
       </c>
       <c r="D339" t="n">
         <v>0.1763511896644202</v>
@@ -6212,10 +6212,10 @@
         <v>45716</v>
       </c>
       <c r="B340" t="n">
-        <v>-0.9279394482883139</v>
+        <v>-0.9466589205079275</v>
       </c>
       <c r="C340" t="n">
-        <v>0.1314508553617306</v>
+        <v>0.1053591485320955</v>
       </c>
       <c r="D340" t="n">
         <v>0.1371594861448566</v>
@@ -6229,16 +6229,33 @@
         <v>45747</v>
       </c>
       <c r="B341" t="n">
-        <v>-0.8870883778336536</v>
+        <v>-0.9152014981959544</v>
       </c>
       <c r="C341" t="n">
-        <v>0.1564856013311842</v>
+        <v>0.08969259728684205</v>
       </c>
       <c r="D341" t="n">
         <v>0.1110546272241258</v>
       </c>
       <c r="E341" t="n">
         <v>-0.1283410707788303</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.8970238361805523</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.07001454885654049</v>
+      </c>
+      <c r="D342" t="n">
+        <v>-0.1433469846859853</v>
+      </c>
+      <c r="E342" t="n">
+        <v>-0.2934007498358872</v>
       </c>
     </row>
   </sheetData>
